--- a/luaran/laporan_akhir/tables/Table1_Dataset_Statistics.xlsx
+++ b/luaran/laporan_akhir/tables/Table1_Dataset_Statistics.xlsx
@@ -29,17 +29,29 @@
       <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003C7A8C"/>
+        <bgColor rgb="003C7A8C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4F8"/>
+        <bgColor rgb="00F0F4F8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -58,25 +70,34 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color rgb="00CBD5E0"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color rgb="00CBD5E0"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color rgb="00CBD5E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color rgb="00CBD5E0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,23 +474,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,86 +495,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Detection
-Train</t>
+          <t>Original_Train</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Detection
-Val</t>
+          <t>Original_Val</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Detection
-Test</t>
+          <t>Original_Test</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Detection
-Total</t>
+          <t>Detection_Aug_Train</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Classification
-Train</t>
+          <t>Classification_Aug_Train</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Classification
-Val</t>
+          <t>Detection_Multiplier</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Classification
-Test</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Classification
-Total</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Aug Det Train</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Aug Cls Train</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Aug Val
-(same)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Aug Test
-(same)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Boxes per
-Image</t>
+          <t>Classification_Multiplier</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IML Lifecycle
-(4 stages)</t>
+          <t>iml_lifecycle</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -572,108 +545,58 @@
         <v>126</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>626</v>
+        <v>1632</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>372</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>626</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>2.0×</t>
+        <v>1305</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>3.5x</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>MD-2019 Stages
-(3 stages)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>md_2019_stages</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>936</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="6" t="n">
         <v>312</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="6" t="n">
         <v>378</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>1626</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>936</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>312</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>378</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>1626</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>2.0×</t>
+      <c r="E3" s="6" t="n">
+        <v>4106</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>3285</v>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MP-IDB Species
-(4 species)</t>
+          <t>mp_idb_species</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -686,100 +609,435 @@
         <v>84</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>418</v>
+        <v>1096</v>
       </c>
       <c r="F4" s="3" t="n">
+        <v>877</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>mp_idb_stages</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>418</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>2.0×</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>MP-IDB Stages
-(4 stages)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="C5" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>877</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>iml_lifecycle</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1632</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1305</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>md_2019_stages</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>936</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>312</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>378</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4106</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>3285</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>mp_idb_species</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>418</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="C8" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>877</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>mp_idb_stages</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>418</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>2.0×</t>
+      <c r="C9" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>877</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>iml_lifecycle</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1632</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1305</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>md_2019_stages</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>936</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>312</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>378</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>4106</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>3285</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>mp_idb_species</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>877</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>mp_idb_stages</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>877</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>iml_lifecycle</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1632</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1305</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>md_2019_stages</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>936</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>312</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>378</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>4106</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3285</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>mp_idb_species</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>877</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>mp_idb_stages</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>877</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>4.4x</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
         </is>
       </c>
     </row>

--- a/luaran/laporan_akhir/tables/Table1_Dataset_Statistics.xlsx
+++ b/luaran/laporan_akhir/tables/Table1_Dataset_Statistics.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -657,390 +657,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>iml_lifecycle</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>372</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1632</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1305</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>md_2019_stages</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>936</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>312</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>378</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>4106</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>3285</v>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>mp_idb_species</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>1096</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>877</v>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>mp_idb_stages</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>250</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>1096</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>877</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>iml_lifecycle</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>372</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1632</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1305</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>md_2019_stages</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>936</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>312</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>378</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>4106</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>3285</v>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>mp_idb_species</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>1096</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>877</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>mp_idb_stages</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>250</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1096</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>877</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>iml_lifecycle</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>372</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>1632</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1305</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>md_2019_stages</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>936</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>312</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>378</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>4106</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>3285</v>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>mp_idb_species</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>1096</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>877</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>mp_idb_stages</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>250</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>1096</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>877</v>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>4.4x</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luaran/laporan_akhir/tables/Table1_Dataset_Statistics.xlsx
+++ b/luaran/laporan_akhir/tables/Table1_Dataset_Statistics.xlsx
@@ -94,7 +94,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -103,7 +103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>iml_lifecycle</t>
+          <t>IML Lifecycle</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -564,7 +564,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>md_2019_stages</t>
+          <t>MD-2019 Stages</t>
         </is>
       </c>
       <c r="B3" s="6" t="n">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>mp_idb_species</t>
+          <t>MP-IDB Species</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -628,7 +628,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>mp_idb_stages</t>
+          <t>MP-IDB Stages</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
